--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чувствительность" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Команда и каюты" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы поставщикам" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +70,9 @@
       <color rgb="005B46B8"/>
       <sz val="13"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,12 +91,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FBF0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EFECFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF0FB"/>
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -143,22 +149,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,15 +534,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки меняем руками. Всё остальное считается формулами. Цены названы поставщиками устно и требуют письменного подтверждения.</t>
+          <t>Жёлтое меняем руками, сиреневое считается само. Цены поставщиков названы устно; цены отелей взяты из открытых источников и предложением не являются.</t>
         </is>
       </c>
     </row>
@@ -585,527 +593,766 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Число гостей</t>
+          <t>Гостей</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>чел</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Фрахт делится на это число</t>
+          <t>На это число делится всё</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Дней фрахта, вариант A</t>
+          <t>Команда La Royal в поездке</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>дней</t>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>чел</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>25–29 января, четыре ночи</t>
+          <t>Их номера, перелёты и питание ложатся на цену гостя</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Дней фрахта, вариант B</t>
+          <t>Команда: человек в номере</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>дней</t>
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>чел</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>25–30 января, пять ночей</t>
+          <t>2 = селим по двое. 1 = одноместно, дороже</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Цена фрахта за день, USD</t>
+          <t>Дней фрахта, вариант A</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>54500</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USD</t>
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>дней</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>ВКЛЮЧАЕТ налоги, чаевые, питание, напитки, гида, билеты — со слов оператора</t>
+          <t>25–29 января</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>Дней фрахта, вариант B</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>дней</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>25–30 января</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Фрахт за день, USD</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>54500</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: за ночь фрахта или за календарный день</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Курс EUR/USD</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <v>1.1489</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Курс на 20.09.2026. На дату платежа будет другим</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>РАСЧЁТ ПО НАЗВАННЫМ ЦЕНАМ</t>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>На 20.09.2026. На дату платежа будет другим</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Вознаграждение La Royal</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>доля</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Наценка на себестоимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>РАСЧЁТ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Колонка «×» показывает, на скольких человек берётся позиция</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Вариант A, на гостя</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Вариант B, на гостя</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>A, на гостя</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>B, на гостя</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Что уточнить</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Фрахт судна</t>
         </is>
       </c>
-      <c r="B14" s="10">
-        <f>$B$9</f>
-        <v/>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B17" s="12">
+        <f>$B$11</f>
+        <v/>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>за день</t>
         </is>
       </c>
-      <c r="D14" s="10">
-        <f>$B$9*$B$7/$B$6</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>$B$9*$B$8/$B$6</f>
-        <v/>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>«В день» — за ночь фрахта или за календарный день? Разница 54 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Филе: приватный визит и показ</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
+      <c r="D17" s="12">
+        <f>$B$11*$B$9/$B$6</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>$B$11*$B$10/$B$6</f>
+        <v/>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: «в день» — за ночь или за календарный день. И входят ли каюты команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Филе: визит и показ</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>EUR за группу</t>
         </is>
       </c>
-      <c r="D15" s="10">
-        <f>B15*$B$10/$B$6</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>B15*$B$10/$B$6</f>
-        <v/>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Договор в евро. Входит ли моторная лодка от Шеллала</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="D18" s="12">
+        <f>B18*$B$12/$B$6</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>B18*$B$12/$B$6</f>
+        <v/>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Договор в евро. Входит ли лодка от Шеллала</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Ужин на острове Филе</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D16" s="10">
-        <f>B16/$B$6</f>
-        <v/>
-      </c>
-      <c r="E16" s="10">
-        <f>B16/$B$6</f>
-        <v/>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>ЦЕНА НЕ НАЗВАНА. Плюсом к 15 000 EUR. Запросить у Мары</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="D19" s="12">
+        <f>B19/$B$6</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>B19/$B$6</f>
+        <v/>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Плюсом к 15 000 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Гиза: приватный доступ, одно посещение</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B20" s="6" t="n">
         <v>3500</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>за посещение</t>
         </is>
       </c>
-      <c r="D17" s="10">
-        <f>B17*2/$B$6</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>B17*2/$B$6</f>
-        <v/>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Нужно ДВА: до открытия и ночью. Ночное может стоить дороже</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="D20" s="12">
+        <f>B20*2/$B$6</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>B20*2/$B$6</f>
+        <v/>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Нужно два. Ночное может быть дороже утреннего</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Абу-Симбел самолётом</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>на человека</t>
+        </is>
+      </c>
+      <c r="D21" s="12">
+        <f>B21*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E21" s="12">
+        <f>B21*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Только перелёт. Билеты и транспорт на месте — отдельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Giza Palace, ночь</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>за номер за ночь</t>
+        </is>
+      </c>
+      <c r="D22" s="12">
+        <f>B22*($B$6*2+ROUNDUP($B$7/$B$8,0)*2)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>B22*($B$6*2+ROUNDUP($B$7/$B$8,0)*2)/$B$6</f>
+        <v/>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Открытые источники 222–349. Запросить групповой тариф</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Steigenberger Nile Palace, ночь</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>за номер за ночь</t>
+        </is>
+      </c>
+      <c r="D23" s="12">
+        <f>B23*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>B23*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <v/>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Four Seasons Cairo, ночь</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>570</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>на человека</t>
+        </is>
+      </c>
+      <c r="D24" s="12">
+        <f>B24*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <v/>
+      </c>
+      <c r="E24" s="12">
+        <f>B24*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <v/>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Названо отелем, все налоги включены</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Ужин в Four Seasons</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B25" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>на человека</t>
         </is>
       </c>
-      <c r="D18" s="10">
-        <f>B18</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
+      <c r="D25" s="12">
+        <f>B25*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E25" s="12">
         <f>0</f>
         <v/>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Net или ++? С 12% сервиса и 14% НДС будет 319. Только вариант A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Ужин в Lucida или руфтоп</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B26" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>на человека</t>
         </is>
       </c>
-      <c r="D19" s="10">
-        <f>B19</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>B19</f>
-        <v/>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Net или ++? С надбавками будет 192</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="D26" s="12">
+        <f>B26*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E26" s="12">
+        <f>B26*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Net или ++? С надбавками 192</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Питание в отелях вне названных ресторанов</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>на человека</t>
+        </is>
+      </c>
+      <c r="D27" s="12">
+        <f>B27*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E27" s="12">
+        <f>B27*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Полёт на шаре</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B28" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>за корзину</t>
         </is>
       </c>
-      <c r="D20" s="10">
-        <f>B20/$B$6</f>
-        <v/>
-      </c>
-      <c r="E20" s="10">
-        <f>B20/$B$6</f>
-        <v/>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Корзина вмещает 8–12. На 16 гостей, вероятно, нужны ДВЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="D28" s="12">
+        <f>B28/$B$6</f>
+        <v/>
+      </c>
+      <c r="E28" s="12">
+        <f>B28/$B$6</f>
+        <v/>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Корзина на 8–12. На 16 гостей, вероятно, нужны ДВЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Нубийский ансамбль</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>за вечер</t>
+        </is>
+      </c>
+      <c r="D29" s="12">
+        <f>B29/$B$6</f>
+        <v/>
+      </c>
+      <c r="E29" s="12">
+        <f>B29/$B$6</f>
+        <v/>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D21" s="10">
+      <c r="D30" s="12">
         <f>0</f>
         <v/>
       </c>
-      <c r="E21" s="10">
-        <f>B21/$B$6</f>
-        <v/>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>ЦЕНА НЕ НАЗВАНА. Меню, декор, музыка сверх пансиона</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="E30" s="12">
+        <f>B30/$B$6</f>
+        <v/>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Наземная программа 22–25 января</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D22" s="10">
-        <f>B22/$B$6</f>
-        <v/>
-      </c>
-      <c r="E22" s="10">
-        <f>B22/$B$6</f>
-        <v/>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>ЦЕНА НЕ НАЗВАНА. Гид, транспорт, билеты, GEM до посадки на судно</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Отели: Giza Palace, Steigenberger, Four Seasons</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
+      <c r="D31" s="12">
+        <f>B31/$B$6</f>
+        <v/>
+      </c>
+      <c r="E31" s="12">
+        <f>B31/$B$6</f>
+        <v/>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM на 20 человек. Крупнейшая дыра</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>за группу</t>
-        </is>
-      </c>
-      <c r="D23" s="10">
-        <f>B23/$B$6</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>B23/$B$6</f>
-        <v/>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>ЦЕНА НЕ НАЗВАНА. 18 номеров × 4 ночи суммарно</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Внутренние перелёты</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>на человека</t>
+        </is>
+      </c>
+      <c r="D32" s="12">
+        <f>B32*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E32" s="12">
+        <f>B32*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Групповой тариф на 20 мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Прочее: Khufu's, Абу-Симбел на месте, meet &amp; greet, чаевые вне судна, страховка</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>на человека</t>
         </is>
       </c>
-      <c r="D24" s="10">
-        <f>B24</f>
-        <v/>
-      </c>
-      <c r="E24" s="10">
-        <f>B24</f>
-        <v/>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>ЦЕНА НЕ НАЗВАНА. CAI–LXR, ASW–ABS–ASW, ASW–CAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Прочее: Khufu's, Абу-Симбел на месте, meet &amp; greet, чаевые вне судна</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>на человека</t>
-        </is>
-      </c>
-      <c r="D25" s="10">
-        <f>B25</f>
-        <v/>
-      </c>
-      <c r="E25" s="10">
-        <f>B25</f>
-        <v/>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>ЦЕНА НЕ НАЗВАНА</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="D33" s="12">
+        <f>B33*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E33" s="12">
+        <f>B33*($B$6+$B$7)/$B$6</f>
+        <v/>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
         </is>
       </c>
-      <c r="D26" s="12">
-        <f>SUM(D14:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="12">
-        <f>SUM(E14:E25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Вознаграждение La Royal, %</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D27" s="10">
-        <f>D26*$B$27</f>
-        <v/>
-      </c>
-      <c r="E27" s="10">
-        <f>E26*$B$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>ЦЕНА ДЛЯ КЛИЕНТА НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D28" s="15">
-        <f>D26+D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="15">
-        <f>E26+E27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>ВНИМАНИЕ: пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
+      <c r="D34" s="13">
+        <f>SUM(D17:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="13">
+        <f>SUM(E17:E33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Вознаграждение La Royal</t>
+        </is>
+      </c>
+      <c r="D35" s="12">
+        <f>D34*$B$13</f>
+        <v/>
+      </c>
+      <c r="E35" s="12">
+        <f>E34*$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>ЦЕНА ДЛЯ ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D36" s="15">
+        <f>D34+D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D37" s="16">
+        <f>D34/(1-$B$13)</f>
+        <v/>
+      </c>
+      <c r="E37" s="16">
+        <f>E34/(1-$B$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Разница между двумя трактовками, на гостя</t>
+        </is>
+      </c>
+      <c r="D38" s="16">
+        <f>D37-D36</f>
+        <v/>
+      </c>
+      <c r="E38" s="16">
+        <f>E37-E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Расходы команды La Royal сидят в СЕБЕСТОИМОСТИ, а не в вознаграждении. Иначе 15 % съедаются на четверть.</t>
         </is>
       </c>
     </row>
@@ -1120,206 +1367,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>КАК ЦЕНА МЕНЯЕТСЯ ОТ ЧИСЛА ГОСТЕЙ</t>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>КОМАНДА LA ROYAL: СКОЛЬКО СТОИТ И СКОЛЬКО КАЮТ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Только по названным ценам. Фрахт — фиксированная сумма, поэтому каждый недобравшийся гость дорожает поездку для остальных.</t>
+          <t>Четыре-пять человек сопровождают группу всю поездку. Для клиента это главное отличие от турпакета, для сметы — отдельная строка.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Число гостей</t>
+          <t>Показатель</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+          <t>Комментарий</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Фрахт, вариант A</t>
-        </is>
-      </c>
-      <c r="B5" s="10">
-        <f>Калькулятор!$B$9*Калькулятор!$B$7/14</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>Калькулятор!$B$9*Калькулятор!$B$7/16</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>Калькулятор!$B$9*Калькулятор!$B$7/18</f>
-        <v/>
-      </c>
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Гостей</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>Калькулятор!$B$6</f>
+        <v/>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Фрахт, вариант B</t>
-        </is>
-      </c>
-      <c r="B6" s="10">
-        <f>Калькулятор!$B$9*Калькулятор!$B$8/14</f>
-        <v/>
-      </c>
-      <c r="C6" s="10">
-        <f>Калькулятор!$B$9*Калькулятор!$B$8/16</f>
-        <v/>
-      </c>
-      <c r="D6" s="10">
-        <f>Калькулятор!$B$9*Калькулятор!$B$8/18</f>
-        <v/>
-      </c>
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Команда La Royal</t>
+        </is>
+      </c>
+      <c r="B6" s="12">
+        <f>Калькулятор!$B$7</f>
+        <v/>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Филе, визит и показ</t>
-        </is>
-      </c>
-      <c r="B7" s="10">
-        <f>15000*Калькулятор!$B$10/14</f>
-        <v/>
-      </c>
-      <c r="C7" s="10">
-        <f>15000*Калькулятор!$B$10/16</f>
-        <v/>
-      </c>
-      <c r="D7" s="10">
-        <f>15000*Калькулятор!$B$10/18</f>
-        <v/>
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Всего человек в пути</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>Калькулятор!$B$6+Калькулятор!$B$7</f>
+        <v/>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Столько мест в самолётах и столько ртов</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Гиза, два посещения</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
-        <f>7000/14</f>
-        <v/>
-      </c>
-      <c r="C8" s="10">
-        <f>7000/16</f>
-        <v/>
-      </c>
-      <c r="D8" s="10">
-        <f>7000/18</f>
-        <v/>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Кают и номеров под команду</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>При размещении по двое</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Шар, одна корзина</t>
-        </is>
-      </c>
-      <c r="B9" s="10">
-        <f>2500/14</f>
-        <v/>
-      </c>
-      <c r="C9" s="10">
-        <f>2500/16</f>
-        <v/>
-      </c>
-      <c r="D9" s="10">
-        <f>2500/18</f>
-        <v/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ВСЕГО КАЮТ НА СУДНЕ</t>
+        </is>
+      </c>
+      <c r="B9" s="20">
+        <f>Калькулятор!$B$6+ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Гости одноместно + команда. ЭТО ТРЕБОВАНИЕ К БОРТУ</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Итого по известному, вариант A</t>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Номера: Giza Palace 2 ночи</t>
         </is>
       </c>
       <c r="B10" s="12">
-        <f>B5+B7+B8+B9+250+150</f>
-        <v/>
-      </c>
-      <c r="C10" s="12">
-        <f>C5+C7+C8+C9+250+150</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>D5+D7+D8+D9+250+150</f>
-        <v/>
-      </c>
+        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)*2*325</f>
+        <v/>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Итого по известному, вариант B</t>
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Номера: Луксор 1 ночь</t>
         </is>
       </c>
       <c r="B11" s="12">
-        <f>B6+B7+B8+B9+150</f>
-        <v/>
-      </c>
-      <c r="C11" s="12">
-        <f>C6+C7+C8+C9+150</f>
-        <v/>
-      </c>
-      <c r="D11" s="12">
-        <f>D6+D7+D8+D9+150</f>
-        <v/>
-      </c>
+        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)*170</f>
+        <v/>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Номера: Four Seasons 1 ночь</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)*570</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Разница между 18 и 14 гостями, вариант A</t>
-        </is>
-      </c>
-      <c r="B13" s="18">
-        <f>B10-D10</f>
-        <v/>
-      </c>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Абу-Симбел самолётом</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>Калькулятор!$B$7*470</f>
+        <v/>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Цена пятого дня на гостя при 16</t>
-        </is>
-      </c>
-      <c r="B14" s="18">
-        <f>C11-C10</f>
-        <v/>
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Ужины Lucida и Four Seasons</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>Калькулятор!$B$7*400</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Питание в отелях</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>Калькулятор!$B$7*200</f>
+        <v/>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ИТОГО расходы на команду, USD</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>SUM(B10:B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>На одного гостя</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>B16/Калькулятор!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Внутренние перелёты команды сюда не входят: цены пока нет.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1333,19 +1592,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>СЕМЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>ДЕВЯТЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
         </is>
       </c>
     </row>
@@ -1367,147 +1626,187 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Сколько денег за этим стоит</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
+          <t>Сколько за этим стоит</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>«54 500 в день» — за ночь фрахта или за календарный день? Считается ли утро высадки оплачиваемым днём?</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Судовой оператор</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>54 500 USD, то есть 3 406 на гостя при 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>54 500, то есть 3 406 на гостя</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Входят ли береговые экскурсии: транспорт, сопровождение, носильщики? И отдельно: дни 22–25 января до посадки в фрахт не входят вовсе</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Судовой оператор + принимающая компания</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>Отдельная строка на 4 дня × 18 человек, сейчас её в смете нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>18–19 кают при 16 гостях и 21 при 18. Входят ли каюты и питание 4–5 сопровождающих в цену или это доплата?</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Судовой оператор</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Определяет, какие борта вообще подходят</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Вместимость корзины шара; сколько корзин покрывают 2 500; летят ли корзины вместе</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Оператор шара</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Вероятно 5 000 вместо 2 500: +156 на гостя</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Наземная программа 22–25 января на 20 человек: гид, транспорт, билеты, GEM</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Принимающая компания</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>Позиции в смете нет вообще</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Гиза: какие зоны, на сколько человек разрешение, длительность окна, съёмка; ночное посещение дороже утреннего?</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Подрядчик спецдоступов</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>3 500 за посещение, двух посещений — 7 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Групповой тариф на 20 мест: Каир — Луксор и Асуан — Каир</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Билетный агент / EgyptAir</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Три рейса × 20 мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Four Seasons и Lucida: цена net или ++ (12 % сервис, 14 % НДС)? Есть ли минимальный счёт за приватную зону сверх меню?</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Отели и ресторан</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>250→319 и 150→192: около 1 800 на группу</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Вместимость корзины шара; сколько корзин покрывают 2 500</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Оператор шара</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Вероятно 5 000 вместо 2 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Филе: фиксируем ли курс EUR/USD; входит ли моторная лодка от Шеллала; цена ужина на острове</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Мара, Egypt &amp; Africa Travel</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Валютный разброс 1 100 на группу + цена ужина</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Гиза: зоны, число человек в разрешении, длительность, съёмка; ночное дороже утреннего?</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Подрядчик спецдоступов</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>7 000 за два посещения</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Что именно входит в «напитки включены»: алкоголь или только безалкогольные?</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Судовой оператор</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Тысячи долларов на 5 днях и 16 гостях</t>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Four Seasons и Lucida: 250 и 150 — net или ++? Минимальный счёт за приватную зону?</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Отели и ресторан</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Около 1 800 на группу</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Филе: фиксируем курс? Входит ли лодка от Шеллала? Цена ужина на острове?</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Мара, Egypt &amp; Africa Travel</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Разброс 1 100 плюс неизвестная</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Групповой блок номеров на январь: Giza Palace и Steigenberger</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Отделы продаж отелей</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Наши 325 и 170 — из интернета, ±30 %</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Команда и каюты" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Команда" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы поставщикам" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,7 +70,14 @@
       <color rgb="005B46B8"/>
       <sz val="13"/>
     </font>
-    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="005B46B8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006E8F13"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -136,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,11 +168,13 @@
     <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -534,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -613,7 +622,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Команда La Royal в поездке</t>
+          <t>Дней фрахта, вариант A</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
@@ -621,524 +630,540 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>чел</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Их номера, перелёты и питание ложатся на цену гостя</t>
+          <t>25–29 января</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Команда: человек в номере</t>
+          <t>Дней фрахта, вариант B</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>чел</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>2 = селим по двое. 1 = одноместно, дороже</t>
+          <t>25–30 января</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Дней фрахта, вариант A</t>
+          <t>Фрахт за день, USD</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4</v>
+        <v>54500</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>дней</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>25–29 января</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: за ночь фрахта или за календарный день</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Дней фрахта, вариант B</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>дней</t>
-        </is>
-      </c>
+          <t>Курс EUR/USD</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>1.1489</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>25–30 января</t>
+          <t>На 20.09.2026. На дату платежа будет другим</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Фрахт за день, USD</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>54500</v>
+          <t>Вознаграждение La Royal</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.15</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>ПРОВЕРИТЬ: за ночь фрахта или за календарный день</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Курс EUR/USD</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>1.1489</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>На 20.09.2026. На дату платежа будет другим</t>
+          <t>доля</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Наценка на себестоимость</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Вознаграждение La Royal</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>доля</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Наценка на себестоимость</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>РАСЧЁТ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Все строки, кроме последней, считаются только по гостям</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>A, на гостя</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>B, на гостя</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Что уточнить</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>РАСЧЁТ</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Колонка «×» показывает, на скольких человек берётся позиция</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Фрахт судна</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>за день</t>
+        </is>
+      </c>
+      <c r="D15" s="12">
+        <f>$B$9*$B$7/$B$6</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>$B$9*$B$8/$B$6</f>
+        <v/>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: «в день» — за ночь фрахта или за календарный день</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Цена</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Единица</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>A, на гостя</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>B, на гостя</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Что уточнить</t>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Филе: визит и показ</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EUR за группу</t>
+        </is>
+      </c>
+      <c r="D16" s="12">
+        <f>B16*$B$10/$B$6</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>B16*$B$10/$B$6</f>
+        <v/>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Договор в евро. Входит ли лодка от Шеллала</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Фрахт судна</t>
-        </is>
-      </c>
-      <c r="B17" s="12">
-        <f>$B$11</f>
-        <v/>
+          <t>Ужин на острове Филе</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>за день</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D17" s="12">
-        <f>$B$11*$B$9/$B$6</f>
+        <f>B17/$B$6</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>$B$11*$B$10/$B$6</f>
+        <f>B17/$B$6</f>
         <v/>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>ПРОВЕРИТЬ: «в день» — за ночь или за календарный день. И входят ли каюты команды</t>
+          <t>ЦЕНЫ НЕТ. Плюсом к 15 000 EUR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Филе: визит и показ</t>
+          <t>Гиза: приватный доступ, одно посещение</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EUR за группу</t>
+          <t>за посещение</t>
         </is>
       </c>
       <c r="D18" s="12">
-        <f>B18*$B$12/$B$6</f>
+        <f>B18*2/$B$6</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>B18*$B$12/$B$6</f>
+        <f>B18*2/$B$6</f>
         <v/>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Договор в евро. Входит ли лодка от Шеллала</t>
+          <t>Нужно два. Ночное может быть дороже утреннего</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Ужин на острове Филе</t>
+          <t>Абу-Симбел самолётом</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D19" s="12">
-        <f>B19/$B$6</f>
+        <f>B19</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>B19/$B$6</f>
-        <v/>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Плюсом к 15 000 EUR</t>
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Только перелёт. Билеты и транспорт на месте — отдельно</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Гиза: приватный доступ, одно посещение</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3500</v>
+        <v>325</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>за посещение</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D20" s="12">
-        <f>B20*2/$B$6</f>
+        <f>B20*2</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>B20*2/$B$6</f>
+        <f>B20*2</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Нужно два. Ночное может быть дороже утреннего</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Абу-Симбел самолётом</t>
+          <t>Steigenberger Nile Palace, ночь</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>на человека</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D21" s="12">
-        <f>B21*($B$6+$B$7)/$B$6</f>
+        <f>B21</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>B21*($B$6+$B$7)/$B$6</f>
+        <f>B21</f>
         <v/>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Только перелёт. Билеты и транспорт на месте — отдельно</t>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Four Seasons Cairo, ночь</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>325</v>
+        <v>570</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D22" s="12">
-        <f>B22*($B$6*2+ROUNDUP($B$7/$B$8,0)*2)/$B$6</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>B22*($B$6*2+ROUNDUP($B$7/$B$8,0)*2)/$B$6</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>Названо отелем, все налоги включены</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D23" s="12">
-        <f>B23*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>B23*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons Cairo, ночь</t>
+          <t>Ужин в Lucida или руфтоп</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>570</v>
+        <v>150</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>на человека</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D24" s="12">
-        <f>B24*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <f>B24</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>B24*($B$6+ROUNDUP($B$7/$B$8,0))/$B$6</f>
+        <f>B24</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Названо отелем, все налоги включены</t>
+          <t>Net или ++? С надбавками 192</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Four Seasons</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>на человека</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D25" s="12">
-        <f>B25*($B$6+$B$7)/$B$6</f>
+        <f>B25</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>0</f>
+        <f>B25</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida или руфтоп</t>
+          <t>Полёт на шаре</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>на человека</t>
+          <t>за корзину</t>
         </is>
       </c>
       <c r="D26" s="12">
-        <f>B26*($B$6+$B$7)/$B$6</f>
+        <f>B26/$B$6</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>B26*($B$6+$B$7)/$B$6</f>
+        <f>B26/$B$6</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 192</t>
+          <t>Корзина на 8–12. На 16 гостей, вероятно, нужны ДВЕ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>на человека</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D27" s="12">
-        <f>B27*($B$6+$B$7)/$B$6</f>
+        <f>B27/$B$6</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>B27*($B$6+$B$7)/$B$6</f>
+        <f>B27/$B$6</f>
         <v/>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>за корзину</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D28" s="12">
-        <f>B28/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E28" s="12">
         <f>B28/$B$6</f>
         <v/>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Корзина на 8–12. На 16 гостей, вероятно, нужны ДВЕ</t>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D29" s="12">
@@ -1149,16 +1174,16 @@
         <f>B29/$B$6</f>
         <v/>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -1166,27 +1191,27 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D30" s="12">
-        <f>0</f>
+        <f>B30</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>B30/$B$6</f>
+        <f>B30</f>
         <v/>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+          <t>ЦЕНЫ НЕТ. Групповой тариф. Места команды — на листе «Команда»</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Прочее: Khufu's, Абу-Симбел на месте, meet &amp; greet, чаевые вне судна, страховка</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -1194,122 +1219,115 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D31" s="12">
-        <f>B31/$B$6</f>
+        <f>B31</f>
         <v/>
       </c>
       <c r="E31" s="12">
-        <f>B31/$B$6</f>
+        <f>B31</f>
         <v/>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM на 20 человек. Крупнейшая дыра</t>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>0</v>
+          <t>КОМАНДА LA ROYAL</t>
+        </is>
+      </c>
+      <c r="B32" s="12">
+        <f>Команда!$B$22</f>
+        <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>на человека</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D32" s="12">
-        <f>B32*($B$6+$B$7)/$B$6</f>
+        <f>B32*Команда!$B$24/$B$6</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>B32*($B$6+$B$7)/$B$6</f>
-        <v/>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Групповой тариф на 20 мест</t>
+        <f>B32*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Прочее: Khufu's, Абу-Симбел на месте, meet &amp; greet, чаевые вне судна, страховка</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>на человека</t>
-        </is>
-      </c>
-      <c r="D33" s="12">
-        <f>B33*($B$6+$B$7)/$B$6</f>
-        <v/>
-      </c>
-      <c r="E33" s="12">
-        <f>B33*($B$6+$B$7)/$B$6</f>
-        <v/>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D33" s="13">
+        <f>SUM(D15:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="13">
+        <f>SUM(E15:E32)</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D34" s="13">
-        <f>SUM(D17:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="13">
-        <f>SUM(E17:E33)</f>
+          <t>Вознаграждение La Royal</t>
+        </is>
+      </c>
+      <c r="D34" s="12">
+        <f>D33*$B$11</f>
+        <v/>
+      </c>
+      <c r="E34" s="12">
+        <f>E33*$B$11</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Вознаграждение La Royal</t>
-        </is>
-      </c>
-      <c r="D35" s="12">
-        <f>D34*$B$13</f>
-        <v/>
-      </c>
-      <c r="E35" s="12">
-        <f>E34*$B$13</f>
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>ЦЕНА ДЛЯ ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D35" s="15">
+        <f>D33+D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
+        <f>E33+E34</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>ЦЕНА ДЛЯ ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D36" s="15">
-        <f>D34+D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="15">
-        <f>E34+E35</f>
-        <v/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D36" s="16">
+        <f>D34*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>E34*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1318,12 +1336,12 @@
           <t>Если 15 % считать долей в цене, а не наценкой</t>
         </is>
       </c>
-      <c r="D37" s="16">
-        <f>D34/(1-$B$13)</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>E34/(1-$B$13)</f>
+      <c r="D37" s="17">
+        <f>D33/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>E33/(1-$B$11)</f>
         <v/>
       </c>
     </row>
@@ -1333,26 +1351,19 @@
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D38" s="16">
-        <f>D37-D36</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>E37-E36</f>
+      <c r="D38" s="17">
+        <f>D37-D35</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>E37-E35</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Расходы команды La Royal сидят в СЕБЕСТОИМОСТИ, а не в вознаграждении. Иначе 15 % съедаются на четверть.</t>
         </is>
       </c>
     </row>
@@ -1367,33 +1378,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>КОМАНДА LA ROYAL: СКОЛЬКО СТОИТ И СКОЛЬКО КАЮТ</t>
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>КОМАНДА LA ROYAL: СВОИ РАСХОДЫ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Четыре-пять человек сопровождают группу всю поездку. Для клиента это главное отличие от турпакета, для сметы — отдельная строка.</t>
+          <t>Четыре-пять человек сопровождают группу всю поездку. На судне живут без доплаты: борт зафрахтован целиком. В Каире размещаются сами. На выезды идут не в полном составе.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Показатель</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1409,175 +1420,297 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Гостей</t>
-        </is>
-      </c>
-      <c r="B5" s="12">
-        <f>Калькулятор!$B$6</f>
-        <v/>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Человек в команде</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Всего в поездке</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>Команда La Royal</t>
-        </is>
-      </c>
-      <c r="B6" s="12">
-        <f>Калькулятор!$B$7</f>
-        <v/>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Человек в номере</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2 = по двое. 1 = одноместно, дороже</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Всего человек в пути</t>
-        </is>
-      </c>
-      <c r="B7" s="12">
-        <f>Калькулятор!$B$6+Калькулятор!$B$7</f>
-        <v/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Едет на выезды</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Столько мест в самолётах и столько ртов</t>
+          <t>Абу-Симбел и рестораны — не весь состав</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Кают и номеров под команду</t>
-        </is>
-      </c>
-      <c r="B8" s="12">
-        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)</f>
-        <v/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Отель в Каире, за номер</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>90</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>При размещении по двое</t>
+          <t>Свой отель, не Giza Palace</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ВСЕГО КАЮТ НА СУДНЕ</t>
-        </is>
-      </c>
-      <c r="B9" s="20">
-        <f>Калькулятор!$B$6+ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Гости одноместно + команда. ЭТО ТРЕБОВАНИЕ К БОРТУ</t>
+          <t>Отель в Луксоре, за номер</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>С группой</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Номера: Giza Palace 2 ночи</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
-        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)*2*325</f>
-        <v/>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Four Seasons, за номер</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>570</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>С группой</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Номера: Луксор 1 ночь</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
-        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)*170</f>
-        <v/>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Номера: Four Seasons 1 ночь</t>
-        </is>
-      </c>
-      <c r="B12" s="12">
-        <f>ROUNDUP(Калькулятор!$B$7/Калькулятор!$B$8,0)*570</f>
-        <v/>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Питание на берегу, на чел</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>За всю поездку. На борту бесплатно</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Как считается</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Судно</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Борт зафрахтован целиком — команда на борту без доплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Каир, свой отель, 2 ночи</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>ROUNDUP($B$5/$B$6,0)*2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Номеров × 2 ночи × цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Луксор, 1 ночь</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>ROUNDUP($B$5/$B$6,0)*$B$9</f>
+        <v/>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Номеров × цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Four Seasons, 1 ночь</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>ROUNDUP($B$5/$B$6,0)*$B$10</f>
+        <v/>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Номеров × цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Абу-Симбел самолётом</t>
         </is>
       </c>
-      <c r="B13" s="12">
-        <f>Калькулятор!$B$7*470</f>
-        <v/>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Ужины Lucida и Four Seasons</t>
-        </is>
-      </c>
-      <c r="B14" s="12">
-        <f>Калькулятор!$B$7*400</f>
-        <v/>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Питание в отелях</t>
-        </is>
-      </c>
-      <c r="B15" s="12">
-        <f>Калькулятор!$B$7*200</f>
-        <v/>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>ИТОГО расходы на команду, USD</t>
-        </is>
-      </c>
-      <c r="B16" s="13">
-        <f>SUM(B10:B15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B18" s="12">
+        <f>$B$7*470</f>
+        <v/>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Летят не все</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Ужины в Lucida и Four Seasons</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>$B$7*400</f>
+        <v/>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>150 + 250 на человека</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Питание на берегу</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>$B$5*$B$11</f>
+        <v/>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Весь состав</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Внутренние перелёты команды</t>
+        </is>
+      </c>
+      <c r="B21" s="12">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Заполнить, когда придёт тариф</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ КОМАНДЫ</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>SUM(B14:B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>На одного гостя</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>B16/Калькулятор!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Внутренние перелёты команды сюда не входят: цены пока нет.</t>
+      <c r="B23" s="16">
+        <f>B22/Калькулятор!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>ПЕРЕКЛЮЧАТЕЛЬ: 1 = в себестоимость, 0 = из вознаграждения</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>1 — клиент платит за сопровождение, не видя отдельной строки. 0 — содержим команду из своей комиссии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Рекомендация: 1. Сопровождение собственной командой — услуга, которая отличает вас от агентства с пакетом. Услуги входят в цену.</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1602,9 +1735,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>ДЕВЯТЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>ВОСЕМЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1777,7 @@
           <t>Судовой оператор</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>54 500, то есть 3 406 на гостя</t>
         </is>
@@ -1656,17 +1789,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>18–19 кают при 16 гостях и 21 при 18. Входят ли каюты и питание 4–5 сопровождающих в цену или это доплата?</t>
+          <t>Наземная программа 22–25 января: гид, транспорт, билеты, GEM</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Судовой оператор</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>Определяет, какие борта вообще подходят</t>
+          <t>Принимающая компания</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Позиции в смете нет вообще</t>
         </is>
       </c>
     </row>
@@ -1676,17 +1809,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января на 20 человек: гид, транспорт, билеты, GEM</t>
+          <t>Групповой тариф: Каир — Луксор и Асуан — Каир</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Принимающая компания</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>Позиции в смете нет вообще</t>
+          <t>Билетный агент / EgyptAir</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Два рейса на всю группу</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1829,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Групповой тариф на 20 мест: Каир — Луксор и Асуан — Каир</t>
+          <t>Вместимость корзины шара; сколько корзин покрывают 2 500</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Билетный агент / EgyptAir</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>Три рейса × 20 мест</t>
+          <t>Оператор шара</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Вероятно 5 000 вместо 2 500</t>
         </is>
       </c>
     </row>
@@ -1716,17 +1849,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Вместимость корзины шара; сколько корзин покрывают 2 500</t>
+          <t>Гиза: зоны, число человек в разрешении, длительность, съёмка; ночное дороже утреннего?</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Оператор шара</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Вероятно 5 000 вместо 2 500</t>
+          <t>Подрядчик спецдоступов</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>7 000 за два посещения</t>
         </is>
       </c>
     </row>
@@ -1736,17 +1869,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Гиза: зоны, число человек в разрешении, длительность, съёмка; ночное дороже утреннего?</t>
+          <t>Four Seasons и Lucida: 250 и 150 — net или ++? Минимальный счёт за приватную зону?</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Подрядчик спецдоступов</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>7 000 за два посещения</t>
+          <t>Отели и ресторан</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Около 1 800 на группу</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1889,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons и Lucida: 250 и 150 — net или ++? Минимальный счёт за приватную зону?</t>
+          <t>Филе: фиксируем курс? Входит ли лодка от Шеллала? Цена ужина на острове?</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Отели и ресторан</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Около 1 800 на группу</t>
+          <t>Мара, Egypt &amp; Africa Travel</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Разброс 1 100 плюс неизвестная</t>
         </is>
       </c>
     </row>
@@ -1776,35 +1909,15 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Филе: фиксируем курс? Входит ли лодка от Шеллала? Цена ужина на острове?</t>
+          <t>Групповой блок номеров на январь: Giza Palace и Steigenberger</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Мара, Egypt &amp; Africa Travel</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>Разброс 1 100 плюс неизвестная</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Групповой блок номеров на январь: Giza Palace и Steigenberger</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
           <t>Отделы продаж отелей</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Наши 325 и 170 — из интернета, ±30 %</t>
         </is>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Нужно два. Ночное может быть дороже утреннего</t>
+          <t>ПОДТВЕРЖДЕНО: персональное разрешение, доступ во все зоны. Нужно два</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 192</t>
+          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
         </is>
       </c>
     </row>
@@ -1071,15 +1071,15 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>за корзину</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D26" s="12">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Корзина на 8–12. На 16 гостей, вероятно, нужны ДВЕ</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1737,7 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>ВОСЕМЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
+          <t>ШЕСТЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
         </is>
       </c>
     </row>
@@ -1829,17 +1829,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Вместимость корзины шара; сколько корзин покрывают 2 500</t>
+          <t>Ужин в Four Seasons: 250 — net или ++? Минимальный счёт за приватную зону сверх меню?</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Оператор шара</t>
+          <t>Four Seasons</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>Вероятно 5 000 вместо 2 500</t>
+          <t>Около 1 100 на группу</t>
         </is>
       </c>
     </row>
@@ -1849,17 +1849,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Гиза: зоны, число человек в разрешении, длительность, съёмка; ночное дороже утреннего?</t>
+          <t>Филе: фиксируем курс? Входит ли лодка от Шеллала? Цена ужина на острове?</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Подрядчик спецдоступов</t>
+          <t>Мара, Egypt &amp; Africa Travel</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>7 000 за два посещения</t>
+          <t>Разброс 1 100 плюс неизвестная</t>
         </is>
       </c>
     </row>
@@ -1869,57 +1869,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons и Lucida: 250 и 150 — net или ++? Минимальный счёт за приватную зону?</t>
+          <t>Групповой блок номеров на январь: Giza Palace и Steigenberger</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Отели и ресторан</t>
+          <t>Отделы продаж отелей</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Около 1 800 на группу</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Филе: фиксируем курс? Входит ли лодка от Шеллала? Цена ужина на острове?</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Мара, Egypt &amp; Africa Travel</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Разброс 1 100 плюс неизвестная</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Групповой блок номеров на январь: Giza Palace и Steigenberger</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Отделы продаж отелей</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>Наши 325 и 170 — из интернета, ±30 %</t>
+          <t>Наши 325 и 170 — из интернета, ±30 %. Письма готовы</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -987,7 +987,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Four Seasons</t>
+          <t>Финальный ужин, MOOD Rooftop Cairo</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>Уточняется. Площадка работает с 22:00 — нужен ранний выкуп. Только вариант A</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -987,7 +987,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Финальный ужин, MOOD Rooftop Cairo</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -1008,14 +1008,14 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Уточняется. Площадка работает с 22:00 — нужен ранний выкуп. Только вариант A</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida или руфтоп</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Four Seasons: 250 — net или ++? Минимальный счёт за приватную зону сверх меню?</t>
+          <t>Прощальный ужин в Four Seasons: 250 — net или ++? Минимальный счёт за приватную зону?</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -63,6 +63,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="006E8F13"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00A85CB0"/>
     </font>
     <font>
@@ -73,10 +77,6 @@
     <font>
       <b val="1"/>
       <color rgb="005B46B8"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="006E8F13"/>
     </font>
   </fonts>
   <fills count="8">
@@ -168,13 +168,13 @@
     <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -875,39 +875,39 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Абу-Симбел самолётом</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>470</v>
+        <v>325</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D19" s="12">
-        <f>B19</f>
+        <f>B19*2</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>B19</f>
+        <f>B19*2</f>
         <v/>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Только перелёт. Билеты и транспорт на месте — отдельно</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Steigenberger Nile Palace, ночь</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>325</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="D20" s="12">
-        <f>B20*2</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>B20*2</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Four Seasons Cairo, ночь</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>170</v>
+        <v>570</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D21" s="12">
@@ -952,18 +952,18 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>Названо отелем, все налоги включены</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons Cairo, ночь</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>570</v>
+        <v>250</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -975,23 +975,23 @@
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>B22</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Названо отелем, все налоги включены</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Прощальный ужин в Four Seasons</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>0</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1036,50 +1036,50 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D25" s="12">
-        <f>B25</f>
+        <f>B25/$B$6</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>B25</f>
+        <f>B25/$B$6</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре, две корзины</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>5000</v>
+        <v>650</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>за все корзины</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D26" s="12">
@@ -1092,42 +1092,42 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D27" s="12">
-        <f>B27/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E27" s="12">
         <f>B27/$B$6</f>
         <v/>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D28" s="12">
-        <f>0</f>
+        <f>B28/$B$6</f>
         <v/>
       </c>
       <c r="E28" s="12">
@@ -1148,14 +1148,14 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -1163,27 +1163,27 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D29" s="12">
-        <f>B29/$B$6</f>
+        <f>B29</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>B29/$B$6</f>
+        <f>B29</f>
         <v/>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
+          <t>ЦЕНЫ НЕТ. Групповой тариф. Места команды — на листе «Команда»</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+          <t>Прочее: Khufu's, meet &amp; greet, fast track</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -1204,14 +1204,14 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Групповой тариф. Места команды — на листе «Команда»</t>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Прочее: Khufu's, Абу-Симбел на месте, meet &amp; greet, чаевые вне судна, страховка</t>
+          <t>Резерв на решения на месте</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -1230,9 +1230,9 @@
         <f>B31</f>
         <v/>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B32" s="12">
-        <f>Команда!$B$22</f>
+        <f>Команда!$B$21</f>
         <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>B32*Команда!$B$24/$B$6</f>
+        <f>B32*Команда!$B$23/$B$6</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>B32*Команда!$B$24/$B$6</f>
+        <f>B32*Команда!$B$23/$B$6</f>
         <v/>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1311,57 +1311,94 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>ОПЦИИ СВЕРХ ПРОГРАММЫ — оплачиваются отдельно, в цену выше не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Абу-Симбел самолётом, на человека</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Летят не все. Билеты и транспорт на месте — цены пока нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Абу-Симбел: билеты и транспорт на месте</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Вознаграждение со всей группы</t>
         </is>
       </c>
-      <c r="D36" s="16">
-        <f>D34*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>E34*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="D40" s="17">
+        <f>D34*$B$6-Команда!$B$21*(1-Команда!$B$23)</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>E34*$B$6-Команда!$B$21*(1-Команда!$B$23)</f>
+        <v/>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Если 15 % считать долей в цене, а не наценкой</t>
         </is>
       </c>
-      <c r="D37" s="17">
+      <c r="D41" s="18">
         <f>D33/(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E37" s="17">
+      <c r="E41" s="18">
         <f>E33/(1-$B$11)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D38" s="17">
-        <f>D37-D35</f>
-        <v/>
-      </c>
-      <c r="E38" s="17">
-        <f>E37-E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="D42" s="18">
+        <f>D41-D35</f>
+        <v/>
+      </c>
+      <c r="E42" s="18">
+        <f>E41-E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>
@@ -1378,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1388,7 +1425,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>КОМАНДА LA ROYAL: СВОИ РАСХОДЫ</t>
         </is>
@@ -1460,7 +1497,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Абу-Симбел и рестораны — не весь состав</t>
+          <t>Рестораны и опции — не весь состав</t>
         </is>
       </c>
     </row>
@@ -1609,106 +1646,90 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Абу-Симбел самолётом</t>
+          <t>Ужины в Lucida и Four Seasons</t>
         </is>
       </c>
       <c r="B18" s="12">
-        <f>$B$7*470</f>
+        <f>$B$7*400</f>
         <v/>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Летят не все</t>
+          <t>150 + 250 на человека</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Ужины в Lucida и Four Seasons</t>
+          <t>Питание на берегу</t>
         </is>
       </c>
       <c r="B19" s="12">
-        <f>$B$7*400</f>
+        <f>$B$5*$B$11</f>
         <v/>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>150 + 250 на человека</t>
+          <t>Весь состав</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Питание на берегу</t>
+          <t>Внутренние перелёты команды</t>
         </is>
       </c>
       <c r="B20" s="12">
-        <f>$B$5*$B$11</f>
-        <v/>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Весь состав</t>
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Заполнить, когда придёт тариф</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Внутренние перелёты команды</t>
-        </is>
-      </c>
-      <c r="B21" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Заполнить, когда придёт тариф</t>
-        </is>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ КОМАНДЫ</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>SUM(B14:B20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ИТОГО РАСХОДЫ КОМАНДЫ</t>
-        </is>
-      </c>
-      <c r="B22" s="13">
-        <f>SUM(B14:B21)</f>
+          <t>На одного гостя</t>
+        </is>
+      </c>
+      <c r="B22" s="17">
+        <f>B21/Калькулятор!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>На одного гостя</t>
-        </is>
-      </c>
-      <c r="B23" s="16">
-        <f>B22/Калькулятор!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>ПЕРЕКЛЮЧАТЕЛЬ: 1 = в себестоимость, 0 = из вознаграждения</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1 — клиент платит за сопровождение, не видя отдельной строки. 0 — содержим команду из своей комиссии.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Рекомендация: 1. Сопровождение собственной командой — услуга, которая отличает вас от агентства с пакетом. Услуги входят в цену.</t>
         </is>
@@ -1735,7 +1756,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>ШЕСТЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
         </is>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Команда" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы поставщикам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Абу-Симбел" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,10 +64,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="006E8F13"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00A85CB0"/>
     </font>
     <font>
@@ -77,6 +74,10 @@
     <font>
       <b val="1"/>
       <color rgb="005B46B8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006E8F13"/>
     </font>
   </fonts>
   <fills count="8">
@@ -143,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,16 +169,18 @@
     <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -875,39 +878,39 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Абу-Симбел самолётом</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D19" s="12">
-        <f>B19*2</f>
+        <f>B19</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>B19*2</f>
+        <f>B19</f>
         <v/>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -915,31 +918,31 @@
         </is>
       </c>
       <c r="D20" s="12">
-        <f>B20</f>
+        <f>B20*2</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>B20</f>
+        <f>B20*2</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons Cairo, ночь</t>
+          <t>Steigenberger Nile Palace, ночь</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>570</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D21" s="12">
@@ -952,18 +955,18 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Названо отелем, все налоги включены</t>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Прощальный ужин в Four Seasons</t>
+          <t>Four Seasons Cairo, ночь</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>250</v>
+        <v>570</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -975,23 +978,23 @@
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>0</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>Названо отелем, все налоги включены</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1003,23 +1006,23 @@
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>B23</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1036,50 +1039,50 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре, две корзины</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>за все корзины</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D25" s="12">
-        <f>B25/$B$6</f>
+        <f>B25</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>B25/$B$6</f>
+        <f>B25</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D26" s="12">
@@ -1092,42 +1095,42 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D27" s="12">
-        <f>0</f>
+        <f>B27/$B$6</f>
         <v/>
       </c>
       <c r="E27" s="12">
         <f>B27/$B$6</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -1139,7 +1142,7 @@
         </is>
       </c>
       <c r="D28" s="12">
-        <f>B28/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E28" s="12">
@@ -1148,14 +1151,14 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -1163,27 +1166,27 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D29" s="12">
-        <f>B29</f>
+        <f>B29/$B$6</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>B29</f>
+        <f>B29/$B$6</f>
         <v/>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Групповой тариф. Места команды — на листе «Команда»</t>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Прочее: Khufu's, meet &amp; greet, fast track</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -1204,14 +1207,14 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ</t>
+          <t>ЦЕНЫ НЕТ. Групповой тариф. Места команды — на листе «Команда»</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Резерв на решения на месте</t>
+          <t>Прочее: Khufu's, meet &amp; greet, fast track</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -1230,175 +1233,166 @@
         <f>B31</f>
         <v/>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
+          <t>Резерв на решения на месте</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>на гостя</t>
+        </is>
+      </c>
+      <c r="D32" s="12">
+        <f>B32</f>
+        <v/>
+      </c>
+      <c r="E32" s="12">
+        <f>B32</f>
+        <v/>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>КОМАНДА LA ROYAL</t>
         </is>
       </c>
-      <c r="B32" s="12">
-        <f>Команда!$B$21</f>
-        <v/>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B33" s="12">
+        <f>Команда!$B$22</f>
+        <v/>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D32" s="12">
-        <f>B32*Команда!$B$23/$B$6</f>
-        <v/>
-      </c>
-      <c r="E32" s="12">
-        <f>B32*Команда!$B$23/$B$6</f>
-        <v/>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="D33" s="12">
+        <f>B33*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E33" s="12">
+        <f>B33*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D33" s="13">
-        <f>SUM(D15:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="13">
-        <f>SUM(E15:E32)</f>
-        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D34" s="13">
+        <f>SUM(D15:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="13">
+        <f>SUM(E15:E33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>Вознаграждение La Royal</t>
         </is>
       </c>
-      <c r="D34" s="12">
-        <f>D33*$B$11</f>
-        <v/>
-      </c>
-      <c r="E34" s="12">
-        <f>E33*$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="D35" s="12">
+        <f>D34*$B$11</f>
+        <v/>
+      </c>
+      <c r="E35" s="12">
+        <f>E34*$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>ЦЕНА ДЛЯ ГОСТЯ</t>
         </is>
       </c>
-      <c r="D35" s="15">
-        <f>D33+D34</f>
-        <v/>
-      </c>
-      <c r="E35" s="15">
-        <f>E33+E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>ОПЦИИ СВЕРХ ПРОГРАММЫ — оплачиваются отдельно, в цену выше не входят</t>
-        </is>
+      <c r="D36" s="15">
+        <f>D34+D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>E34+E35</f>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Абу-Симбел самолётом, на человека</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>470</v>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Летят не все. Билеты и транспорт на месте — цены пока нет</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D37" s="16">
+        <f>D35*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E37" s="16">
+        <f>E35*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Абу-Симбел: билеты и транспорт на месте</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Вознаграждение со всей группы</t>
-        </is>
-      </c>
-      <c r="D40" s="17">
-        <f>D34*$B$6-Команда!$B$21*(1-Команда!$B$23)</f>
-        <v/>
-      </c>
-      <c r="E40" s="17">
-        <f>E34*$B$6-Команда!$B$21*(1-Команда!$B$23)</f>
-        <v/>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
-        </is>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D38" s="17">
+        <f>D34/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>E34/(1-$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Разница между двумя трактовками, на гостя</t>
+        </is>
+      </c>
+      <c r="D39" s="17">
+        <f>D38-D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>E38-E36</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Если 15 % считать долей в цене, а не наценкой</t>
-        </is>
-      </c>
-      <c r="D41" s="18">
-        <f>D33/(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>E33/(1-$B$11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Разница между двумя трактовками, на гостя</t>
-        </is>
-      </c>
-      <c r="D42" s="18">
-        <f>D41-D35</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>E41-E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>
@@ -1415,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1425,7 +1419,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>КОМАНДА LA ROYAL: СВОИ РАСХОДЫ</t>
         </is>
@@ -1497,7 +1491,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Рестораны и опции — не весь состав</t>
+          <t>Абу-Симбел и рестораны — не весь состав</t>
         </is>
       </c>
     </row>
@@ -1646,90 +1640,106 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Ужины в Lucida и Four Seasons</t>
+          <t>Абу-Симбел самолётом</t>
         </is>
       </c>
       <c r="B18" s="12">
-        <f>$B$7*400</f>
+        <f>$B$7*470</f>
         <v/>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>150 + 250 на человека</t>
+          <t>Летят не все</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Питание на берегу</t>
+          <t>Ужины в Lucida и Four Seasons</t>
         </is>
       </c>
       <c r="B19" s="12">
-        <f>$B$5*$B$11</f>
+        <f>$B$7*400</f>
         <v/>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Весь состав</t>
+          <t>150 + 250 на человека</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>Питание на берегу</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>$B$5*$B$11</f>
+        <v/>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Весь состав</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>Внутренние перелёты команды</t>
         </is>
       </c>
-      <c r="B20" s="12">
+      <c r="B21" s="12">
         <f>0</f>
         <v/>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>ЦЕНЫ НЕТ. Заполнить, когда придёт тариф</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ КОМАНДЫ</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <f>SUM(B14:B20)</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>ИТОГО РАСХОДЫ КОМАНДЫ</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>SUM(B14:B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>На одного гостя</t>
         </is>
       </c>
-      <c r="B22" s="17">
-        <f>B21/Калькулятор!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="B23" s="16">
+        <f>B22/Калькулятор!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>ПЕРЕКЛЮЧАТЕЛЬ: 1 = в себестоимость, 0 = из вознаграждения</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B24" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>1 — клиент платит за сопровождение, не видя отдельной строки. 0 — содержим команду из своей комиссии.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Рекомендация: 1. Сопровождение собственной командой — услуга, которая отличает вас от агентства с пакетом. Услуги входят в цену.</t>
         </is>
@@ -1756,7 +1766,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>ШЕСТЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
         </is>
@@ -1901,6 +1911,185 @@
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Наши 325 и 170 — из интернета, ±30 %. Письма готовы</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>АБУ-СИМБЕЛ: САМОЛЁТОМ ИЛИ ПО ЗЕМЛЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Берём обязательной частью для всех. Здесь считается, во что обходится каждый способ и сколько экономит дорога.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Самолётом</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>По земле</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Стоимость перелёта, на человека</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>470 названо поставщиком</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Автобус с гидом на день, за машину</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА 400–800. Нужен запрос в принимающую компанию</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Время в дороге в одну сторону</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Часы. 280–290 км по пустынной трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Весь день занят</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1 = да. По земле день уходит целиком</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>На одного гостя</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C10" s="12">
+        <f>C6/Калькулятор!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ЭКОНОМИЯ ДОРОГИ, на гостя</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ЭКОНОМИЯ ДОРОГИ, на группу</t>
+        </is>
+      </c>
+      <c r="B12" s="25">
+        <f>(B10-C10)*Калькулятор!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Входные билеты в храмы одинаковы в обоих случаях и сидят в наземной программе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>ВНИМАНИЕ: по земле цена ФИКСИРОВАННАЯ за машину. Если делать это опцией, работает та же ловушка, что с шаром: чем меньше едет, тем дороже каждому.</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Команда" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы поставщикам" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Абу-Симбел" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пропущено" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -144,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +182,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1270,129 +1274,158 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
+          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
+        </is>
+      </c>
+      <c r="B33" s="12">
+        <f>Пропущено!$B$19</f>
+        <v/>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>за группу</t>
+        </is>
+      </c>
+      <c r="D33" s="12">
+        <f>B33/$B$6</f>
+        <v/>
+      </c>
+      <c r="E33" s="12">
+        <f>B33/$B$6</f>
+        <v/>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
           <t>КОМАНДА LA ROYAL</t>
         </is>
       </c>
-      <c r="B33" s="12">
+      <c r="B34" s="12">
         <f>Команда!$B$22</f>
         <v/>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D33" s="12">
-        <f>B33*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="E33" s="12">
-        <f>B33*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="D34" s="12">
+        <f>B34*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E34" s="12">
+        <f>B34*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D34" s="13">
-        <f>SUM(D15:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="13">
-        <f>SUM(E15:E33)</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D35" s="13">
+        <f>SUM(D15:D34)</f>
+        <v/>
+      </c>
+      <c r="E35" s="13">
+        <f>SUM(E15:E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Вознаграждение La Royal</t>
         </is>
       </c>
-      <c r="D35" s="12">
-        <f>D34*$B$11</f>
-        <v/>
-      </c>
-      <c r="E35" s="12">
-        <f>E34*$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="D36" s="12">
+        <f>D35*$B$11</f>
+        <v/>
+      </c>
+      <c r="E36" s="12">
+        <f>E35*$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>ЦЕНА ДЛЯ ГОСТЯ</t>
         </is>
       </c>
-      <c r="D36" s="15">
-        <f>D34+D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="15">
-        <f>E34+E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Вознаграждение со всей группы</t>
-        </is>
-      </c>
-      <c r="D37" s="16">
-        <f>D35*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>E35*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
-        </is>
+      <c r="D37" s="15">
+        <f>D35+D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="15">
+        <f>E35+E36</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Если 15 % считать долей в цене, а не наценкой</t>
-        </is>
-      </c>
-      <c r="D38" s="17">
-        <f>D34/(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="E38" s="17">
-        <f>E34/(1-$B$11)</f>
-        <v/>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D38" s="16">
+        <f>D36*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E38" s="16">
+        <f>E36*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D39" s="17">
+        <f>D35/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>E35/(1-$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D39" s="17">
-        <f>D38-D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="17">
-        <f>E38-E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="D40" s="17">
+        <f>D39-D37</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>E39-E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>
@@ -2096,4 +2129,265 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>СТАТЬИ, НАЙДЕННЫЕ ПРИ СВЕРКЕ МАРШРУТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Прошли весь маршрут по дням и сверили с расчётом. Вот чего в нём не было. Заполняйте по мере получения цен — итог сам попадёт в себестоимость.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>USD за группу</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Почему это возникает</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Дневные номера в Асуане 29-го (вариант A)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Судно освобождается в 05:15, рейс в Каир днём. Между ними 18 человек с чемоданами и негде ждать</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Трансферы 29 и 30 января</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Наземная программа посчитана только на 22–25. Асуан и Каир в конце поездки не покрыты</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Багажная машина в дни переездов</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>18 гостей — это 20+ чемоданов. В легковые машины они не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Перевес багажа на внутренних рейсах</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Норма EgyptAir 23 кг. На девятидневной поездке перевес почти гарантирован</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Русскоязычный египтолог на речную часть</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Оператор обещает «гида» — почти наверняка англоязычного. Наш гид 25–29: каюта, питание, гонорар</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Фелюкка и остров Китченера 28-го</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Стоит в программе, в судовой пакет не входит</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Асуан утром 30-го: обелиск, Элефантина, музей</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Только вариант B. Билеты, гид, транспорт</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Абу-Симбел: входные билеты и автобус на месте</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>470 — это только перелёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Банковские комиссии и конвертация</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Платежи в EUR и USD. Обычно 1–3 % от оборота</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Подарки и welcome-набор в номера</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Для поездки такого уровня ожидаемо гостями</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Чаевые береговой части</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Во фрахт входят чаевые ЭКИПАЖУ. Водители, гиды, носильщики и лодочники на берегу — отдельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Фото- и видеосъёмка поездки</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Если нужна. Не обсуждалось</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ИТОГО ПРОПУЩЕНО</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>SUM(B5:B16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>На одного гостя</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>B19/Калькулятор!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Отдельно от этого списка остаются семь крупных позиций на листе «Калькулятор»: наземная программа 22–25, перелёты, ужин на Филе, гала на борту, Khufu's, meet &amp; greet и резерв.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -966,11 +966,11 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons Cairo, ночь</t>
+          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>570</v>
+        <v>250</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>B22</f>
+        <f>570</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Названо отелем, все налоги включены</t>
+          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Four Seasons, за номер</t>
+          <t>Отель 29-го, за номер</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>С группой</t>
+          <t>570 = Four Seasons (B). Для варианта A ставим 250</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Four Seasons, 1 ночь</t>
+          <t>Отель 29-го: Асуан 250 (A) или FS 570 (B)</t>
         </is>
       </c>
       <c r="B17" s="12">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Номеров × цена</t>
+          <t>Номеров × цена. Для A поставить 250</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -1209,9 +1209,9 @@
         <f>B30</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Групповой тариф. Места команды — на листе «Команда»</t>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Заполнить, когда придёт тариф</t>
+        <f>$B$5*250</f>
+        <v/>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Те же 250 на человека</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -830,119 +830,119 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D17" s="12">
-        <f>B17/$B$6</f>
+        <f>B17</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>B17/$B$6</f>
-        <v/>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Плюсом к 15 000 EUR</t>
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Названо клиентом. Сверх 15 000 EUR за приватный вечер</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Гиза: приватный доступ, одно посещение</t>
+          <t>Завтрак в Khufu’s</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3500</v>
+        <v>90</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>за посещение</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D18" s="12">
-        <f>B18*2/$B$6</f>
+        <f>B18</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>B18*2/$B$6</f>
+        <f>B18</f>
         <v/>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: персональное разрешение, доступ во все зоны. Нужно два</t>
+          <t>Названо клиентом</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Абу-Симбел самолётом</t>
+          <t>Гиза: приватный доступ, одно посещение</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>470</v>
+        <v>3500</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за посещение</t>
         </is>
       </c>
       <c r="D19" s="12">
-        <f>B19</f>
+        <f>B19*2/$B$6</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>B19</f>
+        <f>B19*2/$B$6</f>
         <v/>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
+          <t>ПОДТВЕРЖДЕНО: персональное разрешение, доступ во все зоны. Нужно два</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Абу-Симбел самолётом</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D20" s="12">
-        <f>B20*2</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>B20*2</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -950,31 +950,31 @@
         </is>
       </c>
       <c r="D21" s="12">
-        <f>B21</f>
+        <f>B21*2</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>B21</f>
+        <f>B21*2</f>
         <v/>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
+          <t>Steigenberger Nile Palace, ночь</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D22" s="12">
@@ -982,19 +982,19 @@
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>570</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Прощальный ужин в Four Seasons</t>
+          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -1010,23 +1010,23 @@
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>0</f>
+        <f>570</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>B24</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1071,50 +1071,50 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре, две корзины</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>за все корзины</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D26" s="12">
-        <f>B26/$B$6</f>
+        <f>B26</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>B26/$B$6</f>
+        <f>B26</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D27" s="12">
@@ -1127,42 +1127,42 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D28" s="12">
-        <f>0</f>
+        <f>B28/$B$6</f>
         <v/>
       </c>
       <c r="E28" s="12">
         <f>B28/$B$6</f>
         <v/>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="D29" s="12">
-        <f>B29/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E29" s="12">
@@ -1183,46 +1183,46 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D30" s="12">
-        <f>B30</f>
+        <f>B30/$B$6</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>B30</f>
-        <v/>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
+        <f>B30/$B$6</f>
+        <v/>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Прочее: Khufu's, meet &amp; greet, fast track</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -1237,16 +1237,16 @@
         <f>B31</f>
         <v/>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Резерв на решения на месте</t>
+          <t>Прочее: meet &amp; greet, fast track</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -1265,167 +1265,195 @@
         <f>B32</f>
         <v/>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
-        </is>
-      </c>
-      <c r="B33" s="12">
-        <f>Пропущено!$B$19</f>
-        <v/>
+          <t>Резерв на решения на месте</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D33" s="12">
-        <f>B33/$B$6</f>
+        <f>B33</f>
         <v/>
       </c>
       <c r="E33" s="12">
-        <f>B33/$B$6</f>
+        <f>B33</f>
         <v/>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
+          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
+        </is>
+      </c>
+      <c r="B34" s="12">
+        <f>Пропущено!$B$19</f>
+        <v/>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>за группу</t>
+        </is>
+      </c>
+      <c r="D34" s="12">
+        <f>B34/$B$6</f>
+        <v/>
+      </c>
+      <c r="E34" s="12">
+        <f>B34/$B$6</f>
+        <v/>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
           <t>КОМАНДА LA ROYAL</t>
         </is>
       </c>
-      <c r="B34" s="12">
+      <c r="B35" s="12">
         <f>Команда!$B$22</f>
         <v/>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D34" s="12">
-        <f>B34*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="E34" s="12">
-        <f>B34*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="D35" s="12">
+        <f>B35*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E35" s="12">
+        <f>B35*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D35" s="13">
-        <f>SUM(D15:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="13">
-        <f>SUM(E15:E34)</f>
-        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D36" s="13">
+        <f>SUM(D15:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="13">
+        <f>SUM(E15:E35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Вознаграждение La Royal</t>
         </is>
       </c>
-      <c r="D36" s="12">
-        <f>D35*$B$11</f>
-        <v/>
-      </c>
-      <c r="E36" s="12">
-        <f>E35*$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="D37" s="12">
+        <f>D36*$B$11</f>
+        <v/>
+      </c>
+      <c r="E37" s="12">
+        <f>E36*$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>ЦЕНА ДЛЯ ГОСТЯ</t>
         </is>
       </c>
-      <c r="D37" s="15">
-        <f>D35+D36</f>
-        <v/>
-      </c>
-      <c r="E37" s="15">
-        <f>E35+E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Вознаграждение со всей группы</t>
-        </is>
-      </c>
-      <c r="D38" s="16">
-        <f>D36*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>E36*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
-        </is>
+      <c r="D38" s="15">
+        <f>D36+D37</f>
+        <v/>
+      </c>
+      <c r="E38" s="15">
+        <f>E36+E37</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Если 15 % считать долей в цене, а не наценкой</t>
-        </is>
-      </c>
-      <c r="D39" s="17">
-        <f>D35/(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="E39" s="17">
-        <f>E35/(1-$B$11)</f>
-        <v/>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D39" s="16">
+        <f>D37*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E39" s="16">
+        <f>E37*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D40" s="17">
+        <f>D36/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>E36/(1-$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D40" s="17">
-        <f>D39-D37</f>
-        <v/>
-      </c>
-      <c r="E40" s="17">
-        <f>E39-E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="D41" s="17">
+        <f>D40-D38</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>E40-E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>
@@ -1689,16 +1717,16 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Ужины в Lucida и Four Seasons</t>
+          <t>Ужины вне борта: Lucida, Филе, Khufu, прощальный</t>
         </is>
       </c>
       <c r="B19" s="12">
-        <f>$B$7*400</f>
+        <f>$B$7*640</f>
         <v/>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>150 + 250 на человека</t>
+          <t>150+150+90+250 на человека</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -882,95 +882,95 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Гиза: приватный доступ, одно посещение</t>
+          <t>Большой Египетский музей</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3500</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>за посещение</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D19" s="12">
-        <f>B19*2/$B$6</f>
+        <f>B19</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>B19*2/$B$6</f>
+        <f>B19</f>
         <v/>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: персональное разрешение, доступ во все зоны. Нужно два</t>
+          <t>Индивидуальная экскурсия с трансфером. Названо клиентом</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Абу-Симбел самолётом</t>
+          <t>Гиза: приватный доступ, одно посещение</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>470</v>
+        <v>3500</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за посещение</t>
         </is>
       </c>
       <c r="D20" s="12">
-        <f>B20</f>
+        <f>B20*2/$B$6</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>B20</f>
+        <f>B20*2/$B$6</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
+          <t>ПОДТВЕРЖДЕНО: персональное разрешение, доступ во все зоны. Нужно два</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Абу-Симбел самолётом</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D21" s="12">
-        <f>B21*2</f>
+        <f>B21</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>B21*2</f>
+        <f>B21</f>
         <v/>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="D22" s="12">
-        <f>B22</f>
+        <f>B22*2</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>B22</f>
+        <f>B22*2</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
+          <t>Steigenberger Nile Palace, ночь</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D23" s="12">
@@ -1010,19 +1010,19 @@
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>570</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Прощальный ужин в Four Seasons</t>
+          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -1038,23 +1038,23 @@
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>0</f>
+        <f>570</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1066,23 +1066,23 @@
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>B25</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1099,50 +1099,50 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре, две корзины</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>за все корзины</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D27" s="12">
-        <f>B27/$B$6</f>
+        <f>B27</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>B27/$B$6</f>
+        <f>B27</f>
         <v/>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D28" s="12">
@@ -1155,42 +1155,42 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D29" s="12">
-        <f>0</f>
+        <f>B29/$B$6</f>
         <v/>
       </c>
       <c r="E29" s="12">
         <f>B29/$B$6</f>
         <v/>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="D30" s="12">
-        <f>B30/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E30" s="12">
@@ -1211,46 +1211,46 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D31" s="12">
-        <f>B31</f>
+        <f>B31/$B$6</f>
         <v/>
       </c>
       <c r="E31" s="12">
-        <f>B31</f>
-        <v/>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
+        <f>B31/$B$6</f>
+        <v/>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Прочее: meet &amp; greet, fast track</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -1265,16 +1265,16 @@
         <f>B32</f>
         <v/>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Резерв на решения на месте</t>
+          <t>Прочее: meet &amp; greet, fast track</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
@@ -1293,167 +1293,195 @@
         <f>B33</f>
         <v/>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
-        </is>
-      </c>
-      <c r="B34" s="12">
-        <f>Пропущено!$B$19</f>
-        <v/>
+          <t>Резерв на решения на месте</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D34" s="12">
-        <f>B34/$B$6</f>
+        <f>B34</f>
         <v/>
       </c>
       <c r="E34" s="12">
-        <f>B34/$B$6</f>
+        <f>B34</f>
         <v/>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
+          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>Пропущено!$B$19</f>
+        <v/>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>за группу</t>
+        </is>
+      </c>
+      <c r="D35" s="12">
+        <f>B35/$B$6</f>
+        <v/>
+      </c>
+      <c r="E35" s="12">
+        <f>B35/$B$6</f>
+        <v/>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
           <t>КОМАНДА LA ROYAL</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B36" s="12">
         <f>Команда!$B$22</f>
         <v/>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D35" s="12">
-        <f>B35*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="E35" s="12">
-        <f>B35*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="D36" s="12">
+        <f>B36*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E36" s="12">
+        <f>B36*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D36" s="13">
-        <f>SUM(D15:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="13">
-        <f>SUM(E15:E35)</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D37" s="13">
+        <f>SUM(D15:D36)</f>
+        <v/>
+      </c>
+      <c r="E37" s="13">
+        <f>SUM(E15:E36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>Вознаграждение La Royal</t>
         </is>
       </c>
-      <c r="D37" s="12">
-        <f>D36*$B$11</f>
-        <v/>
-      </c>
-      <c r="E37" s="12">
-        <f>E36*$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="D38" s="12">
+        <f>D37*$B$11</f>
+        <v/>
+      </c>
+      <c r="E38" s="12">
+        <f>E37*$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>ЦЕНА ДЛЯ ГОСТЯ</t>
         </is>
       </c>
-      <c r="D38" s="15">
-        <f>D36+D37</f>
-        <v/>
-      </c>
-      <c r="E38" s="15">
-        <f>E36+E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Вознаграждение со всей группы</t>
-        </is>
-      </c>
-      <c r="D39" s="16">
-        <f>D37*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>E37*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
-        </is>
+      <c r="D39" s="15">
+        <f>D37+D38</f>
+        <v/>
+      </c>
+      <c r="E39" s="15">
+        <f>E37+E38</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Если 15 % считать долей в цене, а не наценкой</t>
-        </is>
-      </c>
-      <c r="D40" s="17">
-        <f>D36/(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="E40" s="17">
-        <f>E36/(1-$B$11)</f>
-        <v/>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D40" s="16">
+        <f>D38*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>E38*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D41" s="17">
+        <f>D37/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>E37/(1-$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D41" s="17">
-        <f>D40-D38</f>
-        <v/>
-      </c>
-      <c r="E41" s="17">
-        <f>E40-E38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="D42" s="17">
+        <f>D41-D39</f>
+        <v/>
+      </c>
+      <c r="E42" s="17">
+        <f>E41-E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>
@@ -1721,12 +1749,12 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>$B$7*640</f>
+        <f>$B$7*760</f>
         <v/>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>150+150+90+250 на человека</t>
+          <t>150+150+90+120+250 на человека</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -931,74 +931,74 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: персональное разрешение, доступ во все зоны. Нужно два</t>
+          <t>ПОДТВЕРЖДЕНО: приватное открытие для группы. Билеты НЕ входят, см. строку ниже</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Абу-Симбел самолётом</t>
+          <t>Входной билет на плато Гизы</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>470</v>
+        <v>180</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за билет</t>
         </is>
       </c>
       <c r="D21" s="12">
-        <f>B21</f>
+        <f>B21*2</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>B21</f>
-        <v/>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
+        <f>B21*2</f>
+        <v/>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>180 за билет. ПРОВЕРИТЬ: один билет на оба посещения или два</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Абу-Симбел самолётом</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D22" s="12">
-        <f>B22*2</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>B22*2</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>Обязательная часть для всех. Альтернатива по земле — см. лист «Абу-Симбел»</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1006,31 +1006,31 @@
         </is>
       </c>
       <c r="D23" s="12">
-        <f>B23</f>
+        <f>B23*2</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>B23</f>
+        <f>B23*2</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
+          <t>Steigenberger Nile Palace, ночь</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D24" s="12">
@@ -1038,19 +1038,19 @@
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>570</f>
+        <f>B24</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
+          <t>Открытые источники 120–176. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Прощальный ужин в Four Seasons</t>
+          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -1066,23 +1066,23 @@
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>0</f>
+        <f>570</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1094,23 +1094,23 @@
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>B26</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1127,50 +1127,50 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре, две корзины</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>за все корзины</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D28" s="12">
-        <f>B28/$B$6</f>
+        <f>B28</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>B28/$B$6</f>
+        <f>B28</f>
         <v/>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D29" s="12">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D30" s="12">
-        <f>0</f>
+        <f>B30/$B$6</f>
         <v/>
       </c>
       <c r="E30" s="12">
         <f>B30/$B$6</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D31" s="12">
-        <f>B31/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E31" s="12">
@@ -1239,46 +1239,46 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D32" s="12">
-        <f>B32</f>
+        <f>B32/$B$6</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>B32</f>
-        <v/>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
+        <f>B32/$B$6</f>
+        <v/>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Прочее: meet &amp; greet, fast track</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -1293,16 +1293,16 @@
         <f>B33</f>
         <v/>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Резерв на решения на месте</t>
+          <t>Прочее: meet &amp; greet, fast track</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
@@ -1321,167 +1321,195 @@
         <f>B34</f>
         <v/>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
-        </is>
-      </c>
-      <c r="B35" s="12">
-        <f>Пропущено!$B$19</f>
-        <v/>
+          <t>Резерв на решения на месте</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D35" s="12">
-        <f>B35/$B$6</f>
+        <f>B35</f>
         <v/>
       </c>
       <c r="E35" s="12">
-        <f>B35/$B$6</f>
+        <f>B35</f>
         <v/>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
+          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
+        </is>
+      </c>
+      <c r="B36" s="12">
+        <f>Пропущено!$B$19</f>
+        <v/>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>за группу</t>
+        </is>
+      </c>
+      <c r="D36" s="12">
+        <f>B36/$B$6</f>
+        <v/>
+      </c>
+      <c r="E36" s="12">
+        <f>B36/$B$6</f>
+        <v/>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
           <t>КОМАНДА LA ROYAL</t>
         </is>
       </c>
-      <c r="B36" s="12">
+      <c r="B37" s="12">
         <f>Команда!$B$22</f>
         <v/>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D36" s="12">
-        <f>B36*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="E36" s="12">
-        <f>B36*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="D37" s="12">
+        <f>B37*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E37" s="12">
+        <f>B37*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D37" s="13">
-        <f>SUM(D15:D36)</f>
-        <v/>
-      </c>
-      <c r="E37" s="13">
-        <f>SUM(E15:E36)</f>
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D38" s="13">
+        <f>SUM(D15:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="13">
+        <f>SUM(E15:E37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>Вознаграждение La Royal</t>
         </is>
       </c>
-      <c r="D38" s="12">
-        <f>D37*$B$11</f>
-        <v/>
-      </c>
-      <c r="E38" s="12">
-        <f>E37*$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="D39" s="12">
+        <f>D38*$B$11</f>
+        <v/>
+      </c>
+      <c r="E39" s="12">
+        <f>E38*$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>ЦЕНА ДЛЯ ГОСТЯ</t>
         </is>
       </c>
-      <c r="D39" s="15">
-        <f>D37+D38</f>
-        <v/>
-      </c>
-      <c r="E39" s="15">
-        <f>E37+E38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Вознаграждение со всей группы</t>
-        </is>
-      </c>
-      <c r="D40" s="16">
-        <f>D38*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="E40" s="16">
-        <f>E38*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
-        </is>
+      <c r="D40" s="15">
+        <f>D38+D39</f>
+        <v/>
+      </c>
+      <c r="E40" s="15">
+        <f>E38+E39</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Если 15 % считать долей в цене, а не наценкой</t>
-        </is>
-      </c>
-      <c r="D41" s="17">
-        <f>D37/(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="E41" s="17">
-        <f>E37/(1-$B$11)</f>
-        <v/>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D41" s="16">
+        <f>D39*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E41" s="16">
+        <f>E39*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D42" s="17">
+        <f>D38/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E42" s="17">
+        <f>E38/(1-$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D42" s="17">
-        <f>D41-D39</f>
-        <v/>
-      </c>
-      <c r="E42" s="17">
-        <f>E41-E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="D43" s="17">
+        <f>D42-D40</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>E42-E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>
@@ -1749,12 +1777,12 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>$B$7*760</f>
+        <f>$B$7*760+$B$7*360</f>
         <v/>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>150+150+90+120+250 на человека</t>
+          <t>рестораны 760 + билеты в Гизу 360</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -1873,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1885,7 +1885,7 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>ШЕСТЬ ВОПРОСОВ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
+          <t>ВОПРОСЫ, БЕЗ КОТОРЫХ СЧИТАТЬ НЕЛЬЗЯ</t>
         </is>
       </c>
     </row>
@@ -2028,6 +2028,86 @@
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Наши 325 и 170 — из интернета, ±30 %. Письма готовы</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Сколько кают на нынешнем борту и влезает ли двадцать гостей плюс три каюты команды?</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Судовой оператор</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>На этом держится вся выгода добора до 20: 18 366 вместо 21 814</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Ставка фрахта на борт 22–24 каюты и на борт 35–40 кают, те же даты</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Два-три судовых оператора</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Вилка на 30 гостей 503–572 тыс. Сейчас это наша оценка 75–90 тыс./день</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Сколько корзин шара дают на одну дату и поднимают ли их одновременно?</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Оператор шаров, Луксор</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>На 30 гостей нужны четыре корзины, 2 500 каждая</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Меняется ли цена Филе и открытий в Гизе от размера группы?</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Мара / принимающая компания</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Считаем их постоянными — это 24 тыс. в постоянной части</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -1022,11 +1022,11 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Steigenberger Nile Palace, ночь</t>
+          <t>Sonesta St. George Luxor, ночь</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Открытые источники 120–176. Запросить групповой тариф</t>
+          <t>ПИСЬМО ОТЕЛЯ 22.09: 18 Royal Elite, single BB, сервис и НДС включены. Ужин отдельно</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Групповой блок номеров на январь: Giza Palace и Steigenberger</t>
+          <t>Групповой блок номеров на январь: Giza Palace и Four Seasons</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Наши 325 и 170 — из интернета, ±30 %. Письма готовы</t>
+          <t>325 — из интернета, ±30 %. По Луксору цена есть от отеля</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>На этом держится вся выгода добора до 20: 18 366 вместо 21 814</t>
+          <t>На этом держится вся выгода добора до 20: 18 348 вместо 21 846</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Вилка на 30 гостей 503–572 тыс. Сейчас это наша оценка 75–90 тыс./день</t>
+          <t>Вилка на 30 гостей 504–573 тыс. Сейчас это наша оценка 75–90 тыс./день</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Сколько кают на нынешнем борту и влезает ли двадцать гостей плюс три каюты команды?</t>
+          <t>Подтвердить письменно: 30 кают, сколько продаются в одноместном, где живут экипаж и наша команда</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>На этом держится вся выгода добора до 20: 18 348 вместо 21 846</t>
+          <t>От этого потолок группы: 27 гостей при одноместном размещении</t>
         </is>
       </c>
     </row>
@@ -2057,17 +2057,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ставка фрахта на борт 22–24 каюты и на борт 35–40 кают, те же даты</t>
+          <t>Блоки номеров и места на рейсах под финальное число гостей, а не под 16</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Два-три судовых оператора</t>
+          <t>Отели и авиакомпании</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Вилка на 30 гостей 504–573 тыс. Сейчас это наша оценка 75–90 тыс./день</t>
+          <t>Sonesta дала 18 номеров, на 27 гостей нужно 30. Рейсы в январе кончаются</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>На 30 гостей нужны четыре корзины, 2 500 каждая</t>
+          <t>После 24 гостей нужна четвёртая корзина, 2 500 каждая</t>
         </is>
       </c>
     </row>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150 без алкоголя</t>
+          <t>ПОДТВЕРЖДЕНО: 150, два бокала вина или пива включены</t>
         </is>
       </c>
     </row>
@@ -1843,11 +1843,11 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>ПЕРЕКЛЮЧАТЕЛЬ: 1 = в себестоимость, 0 = из вознаграждения</t>
+          <t>ПЕРЕКЛЮЧАТЕЛЬ: 1 = в себестоимость, 0 = из вознаграждения. РЕШЕНО: 0</t>
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -994,39 +994,39 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Giza Palace, ночь</t>
+          <t>Наземная программа: экскурсии, гиды, доступы в храмы</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>325</v>
+        <v>750</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>за номер за ночь</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D23" s="12">
-        <f>B23*2</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>B23*2</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
+          <t>НАЗВАНО 22.09. Состав уточняется: возможны пересечения с фрахтом, билетами в Гизу и GEM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Sonesta St. George Luxor, ночь</t>
+          <t>Giza Palace, ночь</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>222</v>
+        <v>325</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1034,31 +1034,31 @@
         </is>
       </c>
       <c r="D24" s="12">
-        <f>B24</f>
+        <f>B24*2</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>B24</f>
+        <f>B24*2</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>ПИСЬМО ОТЕЛЯ 22.09: 18 Royal Elite, single BB, сервис и НДС включены. Ужин отдельно</t>
+          <t>Две ночи. Открытые источники 222–349. Запросить групповой тариф</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
+          <t>Sonesta St. George Luxor, ночь</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за номер за ночь</t>
         </is>
       </c>
       <c r="D25" s="12">
@@ -1066,19 +1066,19 @@
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>570</f>
+        <f>B25</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
+          <t>ПИСЬМО ОТЕЛЯ 22.09: 18 Royal Elite, single BB, сервис и НДС включены. Ужин отдельно</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Прощальный ужин в Four Seasons</t>
+          <t>Отель 29 января: Асуан (A) / Four Seasons 30-го (B)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -1094,23 +1094,23 @@
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>0</f>
+        <f>570</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Net или ++? С надбавками 319. Только вариант A</t>
+          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Ужин в Lucida</t>
+          <t>Прощальный ужин в Four Seasons</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1122,23 +1122,23 @@
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>B27</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: 150, два бокала вина или пива включены</t>
+          <t>Net или ++? С надбавками 319. Только вариант A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Питание в отелях вне названных ресторанов</t>
+          <t>Ужин в Lucida</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -1155,50 +1155,50 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
+          <t>ПОДТВЕРЖДЕНО: 150, два бокала вина или пива включены</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Полёт на шаре, две корзины</t>
+          <t>Питание в отелях вне названных ресторанов</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>за все корзины</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D29" s="12">
-        <f>B29/$B$6</f>
+        <f>B29</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>B29/$B$6</f>
+        <f>B29</f>
         <v/>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
+          <t>Наша оценка на всю поездку: ужин 40–60, обед 25–35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Нубийский ансамбль</t>
+          <t>Полёт на шаре, две корзины</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>за вечер</t>
+          <t>за все корзины</t>
         </is>
       </c>
       <c r="D30" s="12">
@@ -1211,42 +1211,42 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Наша оценка 400–900. Публичных прайсов нет</t>
+          <t>ПОДТВЕРЖДЕНО: две корзины, по 8 человек</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Гала-ужин на борту, вариант B</t>
+          <t>Нубийский ансамбль</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>за вечер</t>
         </is>
       </c>
       <c r="D31" s="12">
-        <f>0</f>
+        <f>B31/$B$6</f>
         <v/>
       </c>
       <c r="E31" s="12">
         <f>B31/$B$6</f>
         <v/>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Наша оценка 400–900. Публичных прайсов нет</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Наземная программа 22–25 января</t>
+          <t>Гала-ужин на борту, вариант B</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>B32/$B$6</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E32" s="12">
@@ -1267,46 +1267,46 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
+          <t>ЦЕНЫ НЕТ. Меню, декор, музыка сверх пансиона</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
+          <t>Наземная программа 22–25 января</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>на гостя</t>
+          <t>за группу</t>
         </is>
       </c>
       <c r="D33" s="12">
-        <f>B33</f>
+        <f>B33/$B$6</f>
         <v/>
       </c>
       <c r="E33" s="12">
-        <f>B33</f>
-        <v/>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
+        <f>B33/$B$6</f>
+        <v/>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ. Гид, транспорт, билеты, GEM. Крупнейшая дыра в смете</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Прочее: meet &amp; greet, fast track</t>
+          <t>Перелёты Каир–Луксор и Асуан–Каир</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -1321,16 +1321,16 @@
         <f>B34</f>
         <v/>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА по открытым источникам: 140 + 110. Групповой тариф запрошен</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Резерв на решения на месте</t>
+          <t>Прочее: meet &amp; greet, fast track</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
@@ -1349,167 +1349,195 @@
         <f>B35</f>
         <v/>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
-        </is>
-      </c>
-      <c r="B36" s="12">
-        <f>Пропущено!$B$19</f>
-        <v/>
+          <t>Резерв на решения на месте</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>за группу</t>
+          <t>на гостя</t>
         </is>
       </c>
       <c r="D36" s="12">
-        <f>B36/$B$6</f>
+        <f>B36</f>
         <v/>
       </c>
       <c r="E36" s="12">
-        <f>B36/$B$6</f>
+        <f>B36</f>
         <v/>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+          <t>НЕ ЗАЛОЖЕН. Обычно 2–3 % от сметы. Ваше решение</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
+          <t>ПРОПУЩЕННЫЕ СТАТЬИ — итог с листа «Пропущено»</t>
+        </is>
+      </c>
+      <c r="B37" s="12">
+        <f>Пропущено!$B$19</f>
+        <v/>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>за группу</t>
+        </is>
+      </c>
+      <c r="D37" s="12">
+        <f>B37/$B$6</f>
+        <v/>
+      </c>
+      <c r="E37" s="12">
+        <f>B37/$B$6</f>
+        <v/>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Двенадцать позиций, найденных при сверке. Пока нули</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
           <t>КОМАНДА LA ROYAL</t>
         </is>
       </c>
-      <c r="B37" s="12">
+      <c r="B38" s="12">
         <f>Команда!$B$22</f>
         <v/>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>за группу</t>
         </is>
       </c>
-      <c r="D37" s="12">
-        <f>B37*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="E37" s="12">
-        <f>B37*Команда!$B$24/$B$6</f>
-        <v/>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="D38" s="12">
+        <f>B38*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E38" s="12">
+        <f>B38*Команда!$B$24/$B$6</f>
+        <v/>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Переключатель «в себестоимость / из вознаграждения» — на листе «Команда»</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
-        </is>
-      </c>
-      <c r="D38" s="13">
-        <f>SUM(D15:D37)</f>
-        <v/>
-      </c>
-      <c r="E38" s="13">
-        <f>SUM(E15:E37)</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>СЕБЕСТОИМОСТЬ НА ГОСТЯ</t>
+        </is>
+      </c>
+      <c r="D39" s="13">
+        <f>SUM(D15:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="13">
+        <f>SUM(E15:E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>Вознаграждение La Royal</t>
         </is>
       </c>
-      <c r="D39" s="12">
-        <f>D38*$B$11</f>
-        <v/>
-      </c>
-      <c r="E39" s="12">
-        <f>E38*$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="D40" s="12">
+        <f>D39*$B$11</f>
+        <v/>
+      </c>
+      <c r="E40" s="12">
+        <f>E39*$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>ЦЕНА ДЛЯ ГОСТЯ</t>
         </is>
       </c>
-      <c r="D40" s="15">
-        <f>D38+D39</f>
-        <v/>
-      </c>
-      <c r="E40" s="15">
-        <f>E38+E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Вознаграждение со всей группы</t>
-        </is>
-      </c>
-      <c r="D41" s="16">
-        <f>D39*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="E41" s="16">
-        <f>E39*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
-        <v/>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
-        </is>
+      <c r="D41" s="15">
+        <f>D39+D40</f>
+        <v/>
+      </c>
+      <c r="E41" s="15">
+        <f>E39+E40</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Если 15 % считать долей в цене, а не наценкой</t>
-        </is>
-      </c>
-      <c r="D42" s="17">
-        <f>D38/(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="E42" s="17">
-        <f>E38/(1-$B$11)</f>
-        <v/>
+          <t>Вознаграждение со всей группы</t>
+        </is>
+      </c>
+      <c r="D42" s="16">
+        <f>D40*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="E42" s="16">
+        <f>E40*$B$6-Команда!$B$22*(1-Команда!$B$24)</f>
+        <v/>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Если команда идёт из вознаграждения, её расходы вычитаются здесь</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>Если 15 % считать долей в цене, а не наценкой</t>
+        </is>
+      </c>
+      <c r="D43" s="17">
+        <f>D39/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>E39/(1-$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>Разница между двумя трактовками, на гостя</t>
         </is>
       </c>
-      <c r="D43" s="17">
-        <f>D42-D40</f>
-        <v/>
-      </c>
-      <c r="E43" s="17">
-        <f>E42-E40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="D44" s="17">
+        <f>D43-D41</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f>E43-E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Пока в столбце «Что уточнить» есть розовые строки, итог занижен и клиенту не называется.</t>
         </is>

--- a/egypt-jan-2027/Смета_Египет_2027.xlsx
+++ b/egypt-jan-2027/Смета_Египет_2027.xlsx
@@ -1094,12 +1094,12 @@
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>570</f>
+        <f>550</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 570 названо отелем</t>
+          <t>A: остров Элефантина, открытые источники 140–330. B: Four Seasons, 550 названо отелем</t>
         </is>
       </c>
     </row>
@@ -1677,11 +1677,11 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>570 = Four Seasons (B). Для варианта A ставим 250</t>
+          <t>550 = Four Seasons (B). Для варианта A ставим 250</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Отель 29-го: Асуан 250 (A) или FS 570 (B)</t>
+          <t>Отель 29-го: Асуан 250 (A) или FS 550 (B)</t>
         </is>
       </c>
       <c r="B17" s="12">
